--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434390</v>
+        <v>121434312</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475300</v>
+        <v>475398</v>
       </c>
       <c r="R2" t="n">
-        <v>7144605</v>
+        <v>7144723</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett.</t>
+          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Fjällskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434312</v>
+        <v>121434390</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475398</v>
+        <v>475300</v>
       </c>
       <c r="R3" t="n">
-        <v>7144723</v>
+        <v>7144605</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
+          <t>Tydliga ringhack av Tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Fjällskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121434312</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121434390</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434312</v>
+        <v>121434390</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475398</v>
+        <v>475300</v>
       </c>
       <c r="R2" t="n">
-        <v>7144723</v>
+        <v>7144605</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
+          <t>Tydliga ringhack av Tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Fjällskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434390</v>
+        <v>121434312</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475300</v>
+        <v>475398</v>
       </c>
       <c r="R3" t="n">
-        <v>7144605</v>
+        <v>7144723</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett.</t>
+          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Fjällskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,6 +916,1134 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121536352</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475304</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7144544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121536845</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475736</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7144377</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121536535</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475567</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7144634</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121536398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>475462</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7144663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121536430</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>475508</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7144723</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121536258</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Aron-Aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>475366</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7144547</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121535315</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>475609</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7144719</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hack av tretå.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121536376</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>475462</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7144663</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121536678</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475664</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7144434</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flertalet färska tretåhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121536313</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57354</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aron Aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475355</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7144560</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2045,6 +2045,950 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121550183</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56559</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475609</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7144648</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121549911</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475416</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7144615</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121549762</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475682</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7144544</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121548843</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475702</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7144555</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121548656</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>475616</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7144593</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121549855</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>475536</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7144610</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121549938</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>aron aronsa, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>475457</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7144705</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121548711</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57466</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyslåttjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>475702</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7144662</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökande lavskrikor 2 st.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>A Karlssson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434390</v>
+        <v>121434312</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475300</v>
+        <v>475398</v>
       </c>
       <c r="R2" t="n">
-        <v>7144605</v>
+        <v>7144723</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett.</t>
+          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Fjällskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434312</v>
+        <v>121434390</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475398</v>
+        <v>475300</v>
       </c>
       <c r="R3" t="n">
-        <v>7144723</v>
+        <v>7144605</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
+          <t>Tydliga ringhack av Tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Fjällskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536352</v>
+        <v>121535315</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,17 +959,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475304</v>
+        <v>475609</v>
       </c>
       <c r="R4" t="n">
-        <v>7144544</v>
+        <v>7144719</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +1014,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536845</v>
+        <v>121536313</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,14 +1075,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475736</v>
+        <v>475355</v>
       </c>
       <c r="R5" t="n">
-        <v>7144377</v>
+        <v>7144560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,6 +1125,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1136,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536535</v>
+        <v>121536430</v>
       </c>
       <c r="B6" t="n">
-        <v>79689</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,30 +1162,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475567</v>
+        <v>475508</v>
       </c>
       <c r="R6" t="n">
-        <v>7144634</v>
+        <v>7144723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,9 +1239,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1251,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536398</v>
+        <v>121536535</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,27 +1278,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475462</v>
+        <v>475567</v>
       </c>
       <c r="R7" t="n">
-        <v>7144663</v>
+        <v>7144634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1349,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1358,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536430</v>
+        <v>121536398</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,16 +1393,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475508</v>
+        <v>475462</v>
       </c>
       <c r="R8" t="n">
-        <v>7144723</v>
+        <v>7144663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1461,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,11 +1472,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536258</v>
+        <v>121536845</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,16 +1504,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,22 +1524,18 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475366</v>
+        <v>475736</v>
       </c>
       <c r="R9" t="n">
-        <v>7144547</v>
+        <v>7144377</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,11 +1570,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretå.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1577,11 +1578,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1598,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121535315</v>
+        <v>121536678</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,17 +1634,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475609</v>
+        <v>475664</v>
       </c>
       <c r="R10" t="n">
-        <v>7144719</v>
+        <v>7144434</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,11 +1689,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1714,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536376</v>
+        <v>121536378</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,11 +1796,6 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1825,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536678</v>
+        <v>121536352</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,14 +1851,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475664</v>
+        <v>475304</v>
       </c>
       <c r="R12" t="n">
-        <v>7144434</v>
+        <v>7144544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1895,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536313</v>
+        <v>121536258</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,18 +1958,22 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475355</v>
+        <v>475366</v>
       </c>
       <c r="R13" t="n">
-        <v>7144560</v>
+        <v>7144547</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2166,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549911</v>
+        <v>121548843</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,45 +2177,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475416</v>
+        <v>475702</v>
       </c>
       <c r="R15" t="n">
-        <v>7144615</v>
+        <v>7144555</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,19 +2242,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2281,7 +2272,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549762</v>
+        <v>121549855</v>
       </c>
       <c r="B16" t="n">
         <v>57355</v>
@@ -2329,17 +2320,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475682</v>
+        <v>475536</v>
       </c>
       <c r="R16" t="n">
-        <v>7144544</v>
+        <v>7144610</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2364,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121548843</v>
+        <v>121549938</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,37 +2412,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475702</v>
+        <v>475457</v>
       </c>
       <c r="R17" t="n">
-        <v>7144555</v>
+        <v>7144705</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2488,7 +2484,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,7 +2493,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548656</v>
+        <v>121549762</v>
       </c>
       <c r="B18" t="n">
-        <v>57371</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,16 +2527,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2552,21 +2547,29 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475616</v>
+        <v>475682</v>
       </c>
       <c r="R18" t="n">
-        <v>7144593</v>
+        <v>7144544</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2600,7 +2603,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2635,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549855</v>
+        <v>121549911</v>
       </c>
       <c r="B19" t="n">
         <v>57355</v>
@@ -2670,27 +2673,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475536</v>
+        <v>475416</v>
       </c>
       <c r="R19" t="n">
-        <v>7144610</v>
+        <v>7144615</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,11 +2719,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121549938</v>
+        <v>121548656</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,16 +2766,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2792,22 +2786,18 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475457</v>
+        <v>475616</v>
       </c>
       <c r="R20" t="n">
-        <v>7144705</v>
+        <v>7144593</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2844,7 +2834,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,6 +2845,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121434312</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121434390</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121535315</v>
+        <v>121536535</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>79691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +935,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475609</v>
+        <v>475567</v>
       </c>
       <c r="R4" t="n">
-        <v>7144719</v>
+        <v>7144634</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1015,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536313</v>
+        <v>121536258</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,18 +1070,22 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475355</v>
+        <v>475366</v>
       </c>
       <c r="R5" t="n">
-        <v>7144560</v>
+        <v>7144547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1118,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536430</v>
+        <v>121536678</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,14 +1194,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475508</v>
+        <v>475664</v>
       </c>
       <c r="R6" t="n">
-        <v>7144723</v>
+        <v>7144434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1238,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,11 +1249,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1262,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536535</v>
+        <v>121536430</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,30 +1281,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475567</v>
+        <v>475508</v>
       </c>
       <c r="R7" t="n">
-        <v>7144634</v>
+        <v>7144723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,9 +1358,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536398</v>
+        <v>121536845</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,14 +1421,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475462</v>
+        <v>475736</v>
       </c>
       <c r="R8" t="n">
-        <v>7144663</v>
+        <v>7144377</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,11 +1461,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536845</v>
+        <v>121535315</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,16 +1503,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1528,17 +1527,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475736</v>
+        <v>475609</v>
       </c>
       <c r="R9" t="n">
-        <v>7144377</v>
+        <v>7144719</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1569,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hack av tretå.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1578,6 +1582,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1594,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536678</v>
+        <v>121536378</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,14 +1643,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475664</v>
+        <v>475462</v>
       </c>
       <c r="R10" t="n">
-        <v>7144434</v>
+        <v>7144663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,11 +1683,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536378</v>
+        <v>121536398</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,16 +1725,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1787,6 +1791,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536352</v>
+        <v>121536313</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,14 +1860,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475304</v>
+        <v>475355</v>
       </c>
       <c r="R12" t="n">
-        <v>7144544</v>
+        <v>7144560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,11 +1902,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1906,6 +1910,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536258</v>
+        <v>121536352</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,22 +1967,18 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475366</v>
+        <v>475304</v>
       </c>
       <c r="R13" t="n">
-        <v>7144547</v>
+        <v>7144544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,11 +2026,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121550183</v>
+        <v>121548656</v>
       </c>
       <c r="B14" t="n">
-        <v>56559</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2078,29 +2078,21 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475609</v>
+        <v>475616</v>
       </c>
       <c r="R14" t="n">
-        <v>7144648</v>
+        <v>7144593</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2126,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,6 +2137,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2161,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121548843</v>
+        <v>121549911</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,40 +2174,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R15" t="n">
-        <v>7144555</v>
+        <v>7144615</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,20 +2244,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2272,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549855</v>
+        <v>121548711</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57467</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,20 +2285,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2305,32 +2306,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475536</v>
+        <v>475702</v>
       </c>
       <c r="R16" t="n">
-        <v>7144610</v>
+        <v>7144662</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2361,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549938</v>
+        <v>121549804</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,20 +2431,24 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475457</v>
+        <v>475536</v>
       </c>
       <c r="R17" t="n">
-        <v>7144705</v>
+        <v>7144610</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2484,7 +2485,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,6 +2496,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2514,7 +2520,7 @@
         <v>121549762</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2635,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549911</v>
+        <v>121549938</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,17 +2685,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475416</v>
+        <v>475457</v>
       </c>
       <c r="R19" t="n">
-        <v>7144615</v>
+        <v>7144705</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2721,6 +2727,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2729,11 +2740,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2750,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121548656</v>
+        <v>121548843</v>
       </c>
       <c r="B20" t="n">
-        <v>57371</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,38 +2772,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R20" t="n">
-        <v>7144593</v>
+        <v>7144555</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2834,7 +2839,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,13 +2848,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2866,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121548711</v>
+        <v>121550183</v>
       </c>
       <c r="B21" t="n">
-        <v>57466</v>
+        <v>56560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,20 +2879,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2899,25 +2900,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475702</v>
+        <v>475609</v>
       </c>
       <c r="R21" t="n">
-        <v>7144662</v>
+        <v>7144648</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2954,7 +2959,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,11 +2970,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536535</v>
+        <v>121536678</v>
       </c>
       <c r="B4" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +935,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475567</v>
+        <v>475664</v>
       </c>
       <c r="R4" t="n">
-        <v>7144634</v>
+        <v>7144434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536258</v>
+        <v>121536378</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1070,22 +1066,18 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475366</v>
+        <v>475462</v>
       </c>
       <c r="R5" t="n">
-        <v>7144547</v>
+        <v>7144663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,11 +1112,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretå.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,11 +1120,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1154,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536678</v>
+        <v>121536535</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,38 +1152,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475664</v>
+        <v>475567</v>
       </c>
       <c r="R6" t="n">
-        <v>7144434</v>
+        <v>7144634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1223,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,6 +1232,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1381,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536845</v>
+        <v>121536352</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,16 +1383,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,14 +1407,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475736</v>
+        <v>475304</v>
       </c>
       <c r="R8" t="n">
-        <v>7144377</v>
+        <v>7144544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,6 +1447,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121535315</v>
+        <v>121536313</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1527,17 +1518,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475609</v>
+        <v>475355</v>
       </c>
       <c r="R9" t="n">
-        <v>7144719</v>
+        <v>7144560</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,11 +1558,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536378</v>
+        <v>121536845</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,16 +1605,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1643,14 +1629,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475462</v>
+        <v>475736</v>
       </c>
       <c r="R10" t="n">
-        <v>7144663</v>
+        <v>7144377</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536398</v>
+        <v>121535315</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,16 +1711,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1749,17 +1735,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475462</v>
+        <v>475609</v>
       </c>
       <c r="R11" t="n">
-        <v>7144663</v>
+        <v>7144719</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1779,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,6 +1790,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536313</v>
+        <v>121536258</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1856,18 +1847,22 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475355</v>
+        <v>475366</v>
       </c>
       <c r="R12" t="n">
-        <v>7144560</v>
+        <v>7144547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,6 +1895,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536352</v>
+        <v>121536398</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475304</v>
+        <v>475462</v>
       </c>
       <c r="R13" t="n">
-        <v>7144544</v>
+        <v>7144663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,7 +2158,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549911</v>
+        <v>121549804</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2196,23 +2196,27 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475416</v>
+        <v>475536</v>
       </c>
       <c r="R15" t="n">
-        <v>7144615</v>
+        <v>7144610</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,6 +2246,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121548711</v>
+        <v>121549911</v>
       </c>
       <c r="B16" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,20 +2294,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2306,25 +2315,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R16" t="n">
-        <v>7144662</v>
+        <v>7144615</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2357,11 +2366,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549804</v>
+        <v>121549762</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2441,17 +2445,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475536</v>
+        <v>475682</v>
       </c>
       <c r="R17" t="n">
-        <v>7144610</v>
+        <v>7144544</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2485,7 +2489,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121549762</v>
+        <v>121549938</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2555,27 +2559,23 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475682</v>
+        <v>475457</v>
       </c>
       <c r="R18" t="n">
-        <v>7144544</v>
+        <v>7144705</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,11 +2620,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2641,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549938</v>
+        <v>121548711</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,20 +2648,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2674,28 +2669,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475457</v>
+        <v>475702</v>
       </c>
       <c r="R19" t="n">
-        <v>7144705</v>
+        <v>7144662</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2724,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,6 +2735,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536678</v>
+        <v>121536376</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -959,14 +959,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475664</v>
+        <v>475462</v>
       </c>
       <c r="R4" t="n">
-        <v>7144434</v>
+        <v>7144663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,11 +1001,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1014,6 +1009,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536378</v>
+        <v>121536352</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475462</v>
+        <v>475304</v>
       </c>
       <c r="R5" t="n">
-        <v>7144663</v>
+        <v>7144544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,6 +1110,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536535</v>
+        <v>121536258</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,41 +1157,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475567</v>
+        <v>475366</v>
       </c>
       <c r="R6" t="n">
-        <v>7144634</v>
+        <v>7144547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,9 +1238,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1251,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536430</v>
+        <v>121536845</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,16 +1277,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,14 +1301,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475508</v>
+        <v>475736</v>
       </c>
       <c r="R7" t="n">
-        <v>7144723</v>
+        <v>7144377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,11 +1343,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,11 +1351,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536352</v>
+        <v>121536313</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1407,14 +1407,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475304</v>
+        <v>475355</v>
       </c>
       <c r="R8" t="n">
-        <v>7144544</v>
+        <v>7144560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,11 +1449,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1462,6 +1457,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536313</v>
+        <v>121536398</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,16 +1494,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,14 +1518,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475355</v>
+        <v>475462</v>
       </c>
       <c r="R9" t="n">
-        <v>7144560</v>
+        <v>7144663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,6 +1560,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1568,11 +1573,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536845</v>
+        <v>121536535</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>79691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1605,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475736</v>
+        <v>475567</v>
       </c>
       <c r="R10" t="n">
-        <v>7144377</v>
+        <v>7144634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,12 +1674,18 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1695,7 +1704,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121535315</v>
+        <v>121536430</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1735,17 +1744,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475609</v>
+        <v>475508</v>
       </c>
       <c r="R11" t="n">
-        <v>7144719</v>
+        <v>7144723</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1788,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536258</v>
+        <v>121536678</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1847,22 +1856,18 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475366</v>
+        <v>475664</v>
       </c>
       <c r="R12" t="n">
-        <v>7144547</v>
+        <v>7144434</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,11 +1915,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536398</v>
+        <v>121535315</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1971,17 +1971,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475462</v>
+        <v>475609</v>
       </c>
       <c r="R13" t="n">
-        <v>7144663</v>
+        <v>7144719</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,6 +2026,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121548656</v>
+        <v>121548711</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57467</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,20 +2059,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2075,24 +2080,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R14" t="n">
-        <v>7144593</v>
+        <v>7144662</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549804</v>
+        <v>121550183</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,16 +2183,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2196,7 +2205,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2206,17 +2215,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475536</v>
+        <v>475609</v>
       </c>
       <c r="R15" t="n">
-        <v>7144610</v>
+        <v>7144648</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,7 +2259,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,11 +2270,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2282,10 +2286,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549911</v>
+        <v>121548843</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,45 +2302,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475416</v>
+        <v>475702</v>
       </c>
       <c r="R16" t="n">
-        <v>7144615</v>
+        <v>7144555</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,19 +2367,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548711</v>
+        <v>121549911</v>
       </c>
       <c r="B19" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,20 +2648,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2669,25 +2669,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R19" t="n">
-        <v>7144662</v>
+        <v>7144615</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2720,11 +2720,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121548843</v>
+        <v>121548656</v>
       </c>
       <c r="B20" t="n">
-        <v>79691</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,37 +2767,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475702</v>
+        <v>475616</v>
       </c>
       <c r="R20" t="n">
-        <v>7144555</v>
+        <v>7144593</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2839,7 +2835,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,9 +2844,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121550183</v>
+        <v>121549855</v>
       </c>
       <c r="B21" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,16 +2883,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2905,7 +2905,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475609</v>
+        <v>475536</v>
       </c>
       <c r="R21" t="n">
-        <v>7144648</v>
+        <v>7144610</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,6 +2970,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536376</v>
+        <v>121536258</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -955,18 +955,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R4" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,6 +1003,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536352</v>
+        <v>121536378</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1074,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475304</v>
+        <v>475462</v>
       </c>
       <c r="R5" t="n">
-        <v>7144544</v>
+        <v>7144663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,11 +1119,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536258</v>
+        <v>121536398</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,16 +1161,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1177,22 +1181,18 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475366</v>
+        <v>475462</v>
       </c>
       <c r="R6" t="n">
-        <v>7144547</v>
+        <v>7144663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,11 +1240,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1367,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536313</v>
+        <v>121536352</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1407,14 +1402,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475355</v>
+        <v>475304</v>
       </c>
       <c r="R8" t="n">
-        <v>7144560</v>
+        <v>7144544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1457,11 +1457,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536398</v>
+        <v>121536678</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,16 +1489,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,14 +1513,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475462</v>
+        <v>475664</v>
       </c>
       <c r="R9" t="n">
-        <v>7144663</v>
+        <v>7144434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1557,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536535</v>
+        <v>121536430</v>
       </c>
       <c r="B10" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,30 +1600,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1636,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475567</v>
+        <v>475508</v>
       </c>
       <c r="R10" t="n">
-        <v>7144634</v>
+        <v>7144723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,9 +1677,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1704,7 +1700,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536430</v>
+        <v>121536313</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1744,14 +1740,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475508</v>
+        <v>475355</v>
       </c>
       <c r="R11" t="n">
-        <v>7144723</v>
+        <v>7144560</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,11 +1780,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536678</v>
+        <v>121535315</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1860,17 +1851,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475664</v>
+        <v>475609</v>
       </c>
       <c r="R12" t="n">
-        <v>7144434</v>
+        <v>7144719</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,6 +1906,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1931,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121535315</v>
+        <v>121536535</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>79691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,41 +1943,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475609</v>
+        <v>475567</v>
       </c>
       <c r="R13" t="n">
-        <v>7144719</v>
+        <v>7144634</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,13 +2023,9 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2047,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121548711</v>
+        <v>121549855</v>
       </c>
       <c r="B14" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,20 +2054,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2080,28 +2075,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475702</v>
+        <v>475536</v>
       </c>
       <c r="R14" t="n">
-        <v>7144662</v>
+        <v>7144610</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,7 +2134,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121550183</v>
+        <v>121549911</v>
       </c>
       <c r="B15" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,16 +2182,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2208,21 +2207,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475609</v>
+        <v>475416</v>
       </c>
       <c r="R15" t="n">
-        <v>7144648</v>
+        <v>7144615</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2257,11 +2252,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2270,6 +2260,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2286,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121548843</v>
+        <v>121549762</v>
       </c>
       <c r="B16" t="n">
-        <v>79691</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,40 +2297,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475702</v>
+        <v>475682</v>
       </c>
       <c r="R16" t="n">
-        <v>7144555</v>
+        <v>7144544</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2373,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,9 +2382,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2397,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549762</v>
+        <v>121549938</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2435,27 +2443,23 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475682</v>
+        <v>475457</v>
       </c>
       <c r="R17" t="n">
-        <v>7144544</v>
+        <v>7144705</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2493,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,11 +2504,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2521,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121549938</v>
+        <v>121548656</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2557,22 +2556,18 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475457</v>
+        <v>475616</v>
       </c>
       <c r="R18" t="n">
-        <v>7144705</v>
+        <v>7144593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,6 +2615,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549911</v>
+        <v>121550183</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,16 +2652,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2677,17 +2677,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475416</v>
+        <v>475609</v>
       </c>
       <c r="R19" t="n">
-        <v>7144615</v>
+        <v>7144648</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2722,6 +2726,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2730,11 +2739,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2751,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121548656</v>
+        <v>121548843</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,38 +2771,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R20" t="n">
-        <v>7144593</v>
+        <v>7144555</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2835,7 +2838,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,13 +2847,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2867,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121549855</v>
+        <v>121548711</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,20 +2878,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2900,32 +2899,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475536</v>
+        <v>475702</v>
       </c>
       <c r="R21" t="n">
-        <v>7144610</v>
+        <v>7144662</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2959,7 +2954,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549938</v>
+        <v>121550183</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2446,20 +2446,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475457</v>
+        <v>475609</v>
       </c>
       <c r="R17" t="n">
-        <v>7144705</v>
+        <v>7144648</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,7 +2497,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548656</v>
+        <v>121549938</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,16 +2540,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,18 +2560,22 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475616</v>
+        <v>475457</v>
       </c>
       <c r="R18" t="n">
-        <v>7144593</v>
+        <v>7144705</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2604,7 +2612,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,11 +2623,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2636,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121550183</v>
+        <v>121548656</v>
       </c>
       <c r="B19" t="n">
-        <v>56560</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,16 +2655,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2672,29 +2675,21 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475609</v>
+        <v>475616</v>
       </c>
       <c r="R19" t="n">
-        <v>7144648</v>
+        <v>7144593</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2728,7 +2723,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,6 +2734,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121550183</v>
+        <v>121549938</v>
       </c>
       <c r="B17" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2446,24 +2446,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475609</v>
+        <v>475457</v>
       </c>
       <c r="R17" t="n">
-        <v>7144648</v>
+        <v>7144705</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2497,7 +2493,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121549938</v>
+        <v>121548656</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2540,16 +2536,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2560,22 +2556,18 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475457</v>
+        <v>475616</v>
       </c>
       <c r="R18" t="n">
-        <v>7144705</v>
+        <v>7144593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2612,7 +2604,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,6 +2615,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2639,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548656</v>
+        <v>121550183</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>56560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,16 +2652,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2675,21 +2672,29 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475616</v>
+        <v>475609</v>
       </c>
       <c r="R19" t="n">
-        <v>7144593</v>
+        <v>7144648</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2723,7 +2728,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,11 +2739,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434312</v>
+        <v>121434390</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475398</v>
+        <v>475300</v>
       </c>
       <c r="R2" t="n">
-        <v>7144723</v>
+        <v>7144605</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
+          <t>Tydliga ringhack av Tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Fjällskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434390</v>
+        <v>121434312</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475300</v>
+        <v>475398</v>
       </c>
       <c r="R3" t="n">
-        <v>7144605</v>
+        <v>7144723</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tydliga ringhack av Tretåig hackspett.</t>
+          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Fjällskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536258</v>
+        <v>121536352</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,22 +955,18 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475366</v>
+        <v>475304</v>
       </c>
       <c r="R4" t="n">
-        <v>7144547</v>
+        <v>7144544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,11 +1014,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1039,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536378</v>
+        <v>121536845</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,14 +1070,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475462</v>
+        <v>475736</v>
       </c>
       <c r="R5" t="n">
-        <v>7144663</v>
+        <v>7144377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536398</v>
+        <v>121536430</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475462</v>
+        <v>475508</v>
       </c>
       <c r="R6" t="n">
-        <v>7144663</v>
+        <v>7144723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,6 +1231,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1256,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536845</v>
+        <v>121536313</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,16 +1268,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1296,14 +1292,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475736</v>
+        <v>475355</v>
       </c>
       <c r="R7" t="n">
-        <v>7144377</v>
+        <v>7144560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,6 +1342,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1362,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536352</v>
+        <v>121536535</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>79698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,27 +1379,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475304</v>
+        <v>475567</v>
       </c>
       <c r="R8" t="n">
-        <v>7144544</v>
+        <v>7144634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1450,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,6 +1459,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536678</v>
+        <v>121536378</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,14 +1518,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475664</v>
+        <v>475462</v>
       </c>
       <c r="R9" t="n">
-        <v>7144434</v>
+        <v>7144663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,11 +1558,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536430</v>
+        <v>121536398</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475508</v>
+        <v>475462</v>
       </c>
       <c r="R10" t="n">
-        <v>7144723</v>
+        <v>7144663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,11 +1679,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536313</v>
+        <v>121536678</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,14 +1735,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475355</v>
+        <v>475664</v>
       </c>
       <c r="R11" t="n">
-        <v>7144560</v>
+        <v>7144434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,6 +1777,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flertalet färska tretåhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1790,11 +1790,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1811,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121535315</v>
+        <v>121536258</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,21 +1842,25 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475609</v>
+        <v>475366</v>
       </c>
       <c r="R12" t="n">
-        <v>7144719</v>
+        <v>7144547</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1894,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536535</v>
+        <v>121535315</v>
       </c>
       <c r="B13" t="n">
-        <v>79691</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,44 +1942,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475567</v>
+        <v>475609</v>
       </c>
       <c r="R13" t="n">
-        <v>7144634</v>
+        <v>7144719</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,9 +2019,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549855</v>
+        <v>121548843</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,46 +2058,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475536</v>
+        <v>475702</v>
       </c>
       <c r="R14" t="n">
-        <v>7144610</v>
+        <v>7144555</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2134,7 +2125,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack både färska och äldre samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,13 +2134,9 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2166,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549911</v>
+        <v>121548656</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,16 +2169,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2202,11 +2189,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2214,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475416</v>
+        <v>475616</v>
       </c>
       <c r="R15" t="n">
-        <v>7144615</v>
+        <v>7144593</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,6 +2233,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549762</v>
+        <v>121549804</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,17 +2317,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475682</v>
+        <v>475536</v>
       </c>
       <c r="R16" t="n">
-        <v>7144544</v>
+        <v>7144610</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2361,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549938</v>
+        <v>121549762</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,23 +2431,27 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475457</v>
+        <v>475682</v>
       </c>
       <c r="R17" t="n">
-        <v>7144705</v>
+        <v>7144544</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,7 +2485,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,6 +2496,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2520,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548656</v>
+        <v>121549911</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,16 +2533,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2556,7 +2553,11 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2564,13 +2565,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475616</v>
+        <v>475416</v>
       </c>
       <c r="R18" t="n">
-        <v>7144593</v>
+        <v>7144615</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2600,11 +2601,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121550183</v>
+        <v>121548711</v>
       </c>
       <c r="B19" t="n">
-        <v>56560</v>
+        <v>57468</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,20 +2644,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2669,29 +2665,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475609</v>
+        <v>475702</v>
       </c>
       <c r="R19" t="n">
-        <v>7144648</v>
+        <v>7144662</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2728,7 +2720,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,6 +2731,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2755,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121548843</v>
+        <v>121549938</v>
       </c>
       <c r="B20" t="n">
-        <v>79691</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,37 +2768,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475702</v>
+        <v>475457</v>
       </c>
       <c r="R20" t="n">
-        <v>7144555</v>
+        <v>7144705</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2838,7 +2840,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,7 +2849,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2866,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121548711</v>
+        <v>121550183</v>
       </c>
       <c r="B21" t="n">
-        <v>57467</v>
+        <v>56561</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,20 +2879,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2899,25 +2900,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475702</v>
+        <v>475609</v>
       </c>
       <c r="R21" t="n">
-        <v>7144662</v>
+        <v>7144648</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2954,7 +2959,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,11 +2970,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536430</v>
+        <v>121536845</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,14 +959,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475508</v>
+        <v>475736</v>
       </c>
       <c r="R4" t="n">
-        <v>7144723</v>
+        <v>7144377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,11 +1001,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1014,11 +1009,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1035,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536258</v>
+        <v>121535315</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1071,25 +1061,21 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475366</v>
+        <v>475609</v>
       </c>
       <c r="R5" t="n">
-        <v>7144547</v>
+        <v>7144719</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536378</v>
+        <v>121536398</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,16 +1157,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1237,6 +1223,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1261,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536398</v>
+        <v>121536258</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,16 +1268,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1297,18 +1288,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R7" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1351,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536535</v>
+        <v>121536376</v>
       </c>
       <c r="B8" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,30 +1388,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1419,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475567</v>
+        <v>475462</v>
       </c>
       <c r="R8" t="n">
-        <v>7144634</v>
+        <v>7144663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,20 +1454,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1487,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536313</v>
+        <v>121536535</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,38 +1499,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475355</v>
+        <v>475567</v>
       </c>
       <c r="R9" t="n">
-        <v>7144560</v>
+        <v>7144634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,19 +1568,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536845</v>
+        <v>121536352</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1638,14 +1638,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475736</v>
+        <v>475304</v>
       </c>
       <c r="R10" t="n">
-        <v>7144377</v>
+        <v>7144544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,6 +1678,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536678</v>
+        <v>121536313</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1744,14 +1749,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475664</v>
+        <v>475355</v>
       </c>
       <c r="R11" t="n">
-        <v>7144434</v>
+        <v>7144560</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1799,6 +1799,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1815,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121535315</v>
+        <v>121536678</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1855,17 +1860,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475609</v>
+        <v>475664</v>
       </c>
       <c r="R12" t="n">
-        <v>7144719</v>
+        <v>7144434</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,7 +1904,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,11 +1915,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1931,7 +1931,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536352</v>
+        <v>121536430</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475304</v>
+        <v>475508</v>
       </c>
       <c r="R13" t="n">
-        <v>7144544</v>
+        <v>7144723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,6 +2026,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2157,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549762</v>
+        <v>121550183</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,16 +2178,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2195,7 +2200,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2209,13 +2214,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475682</v>
+        <v>475609</v>
       </c>
       <c r="R15" t="n">
-        <v>7144544</v>
+        <v>7144648</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,11 +2265,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121548843</v>
+        <v>121548656</v>
       </c>
       <c r="B17" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,37 +2412,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475702</v>
+        <v>475616</v>
       </c>
       <c r="R17" t="n">
-        <v>7144555</v>
+        <v>7144593</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,7 +2480,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,9 +2489,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2507,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121549804</v>
+        <v>121548711</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,20 +2524,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2540,32 +2545,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475536</v>
+        <v>475702</v>
       </c>
       <c r="R18" t="n">
-        <v>7144610</v>
+        <v>7144662</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2600,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548656</v>
+        <v>121549762</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,16 +2648,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2667,21 +2668,29 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475616</v>
+        <v>475682</v>
       </c>
       <c r="R19" t="n">
-        <v>7144593</v>
+        <v>7144544</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,7 +2724,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121550183</v>
+        <v>121549804</v>
       </c>
       <c r="B20" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,16 +2772,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2785,7 +2794,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2795,17 +2804,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475609</v>
+        <v>475536</v>
       </c>
       <c r="R20" t="n">
-        <v>7144648</v>
+        <v>7144610</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2839,7 +2848,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,6 +2859,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2866,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121548711</v>
+        <v>121548843</v>
       </c>
       <c r="B21" t="n">
-        <v>57468</v>
+        <v>79698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,35 +2892,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2917,10 +2926,10 @@
         <v>475702</v>
       </c>
       <c r="R21" t="n">
-        <v>7144662</v>
+        <v>7144555</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,7 +2963,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,13 +2972,9 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536398</v>
+        <v>121536258</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1177,18 +1177,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R6" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1240,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1252,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536258</v>
+        <v>121536398</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,16 +1277,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1288,22 +1297,18 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475366</v>
+        <v>475462</v>
       </c>
       <c r="R7" t="n">
-        <v>7144547</v>
+        <v>7144663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,11 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121548656</v>
+        <v>121548711</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>57468</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,20 +2408,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2429,24 +2429,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R17" t="n">
-        <v>7144593</v>
+        <v>7144662</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,7 +2484,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548711</v>
+        <v>121548656</v>
       </c>
       <c r="B18" t="n">
-        <v>57468</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,20 +2528,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2545,28 +2549,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475702</v>
+        <v>475616</v>
       </c>
       <c r="R18" t="n">
-        <v>7144662</v>
+        <v>7144593</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549762</v>
+        <v>121548843</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,49 +2648,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475682</v>
+        <v>475702</v>
       </c>
       <c r="R19" t="n">
-        <v>7144544</v>
+        <v>7144555</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2724,7 +2715,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Bohål av möjlig tretåig hackspett. Bohål i gammal sälg.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,13 +2724,9 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2753,241 +2740,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>121549804</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Aron aronsa, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>475536</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7144610</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bo i gammal sälg möjlig tretåig hackspett. Stort antal ringhack samt andra spår av Tretå i området kring bohålan.</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>121548843</v>
-      </c>
-      <c r="B21" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Nyslåttjärnarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>475702</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7144555</v>
-      </c>
-      <c r="S21" t="n">
-        <v>25</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>A Karlssson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536845</v>
+        <v>121536376</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,14 +959,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475736</v>
+        <v>475462</v>
       </c>
       <c r="R4" t="n">
-        <v>7144377</v>
+        <v>7144663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,6 +1009,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121535315</v>
+        <v>121536258</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1061,21 +1066,25 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475609</v>
+        <v>475366</v>
       </c>
       <c r="R5" t="n">
-        <v>7144719</v>
+        <v>7144547</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536258</v>
+        <v>121536430</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1177,22 +1186,18 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475366</v>
+        <v>475508</v>
       </c>
       <c r="R6" t="n">
-        <v>7144547</v>
+        <v>7144723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536376</v>
+        <v>121536313</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1412,14 +1417,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475462</v>
+        <v>475355</v>
       </c>
       <c r="R8" t="n">
-        <v>7144663</v>
+        <v>7144560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536535</v>
+        <v>121535315</v>
       </c>
       <c r="B9" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,44 +1504,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475567</v>
+        <v>475609</v>
       </c>
       <c r="R9" t="n">
-        <v>7144634</v>
+        <v>7144719</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1572,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,9 +1581,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1598,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536352</v>
+        <v>121536845</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,16 +1620,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1638,14 +1644,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475304</v>
+        <v>475736</v>
       </c>
       <c r="R10" t="n">
-        <v>7144544</v>
+        <v>7144377</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,11 +1684,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536313</v>
+        <v>121536535</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,38 +1726,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475355</v>
+        <v>475567</v>
       </c>
       <c r="R11" t="n">
-        <v>7144560</v>
+        <v>7144634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,19 +1795,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536678</v>
+        <v>121536352</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1860,14 +1865,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475664</v>
+        <v>475304</v>
       </c>
       <c r="R12" t="n">
-        <v>7144434</v>
+        <v>7144544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1909,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536430</v>
+        <v>121536678</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1971,14 +1976,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475508</v>
+        <v>475664</v>
       </c>
       <c r="R13" t="n">
-        <v>7144723</v>
+        <v>7144434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,11 +2031,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121550183</v>
+        <v>121548656</v>
       </c>
       <c r="B15" t="n">
-        <v>56561</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,16 +2178,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2198,29 +2198,21 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475609</v>
+        <v>475616</v>
       </c>
       <c r="R15" t="n">
-        <v>7144648</v>
+        <v>7144593</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,6 +2257,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2281,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549911</v>
+        <v>121548843</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,45 +2294,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475416</v>
+        <v>475702</v>
       </c>
       <c r="R16" t="n">
-        <v>7144615</v>
+        <v>7144555</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,19 +2359,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2396,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121548711</v>
+        <v>121549911</v>
       </c>
       <c r="B17" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,20 +2401,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2429,25 +2422,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R17" t="n">
-        <v>7144662</v>
+        <v>7144615</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2480,11 +2473,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548656</v>
+        <v>121550183</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,16 +2520,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2552,21 +2540,29 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475616</v>
+        <v>475609</v>
       </c>
       <c r="R18" t="n">
-        <v>7144593</v>
+        <v>7144648</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2600,7 +2596,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,11 +2607,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2632,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548843</v>
+        <v>121548711</v>
       </c>
       <c r="B19" t="n">
-        <v>79698</v>
+        <v>57468</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,30 +2635,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2678,10 +2674,10 @@
         <v>475702</v>
       </c>
       <c r="R19" t="n">
-        <v>7144555</v>
+        <v>7144662</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,7 +2711,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,9 +2720,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536376</v>
+        <v>121535315</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -959,17 +959,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475462</v>
+        <v>475609</v>
       </c>
       <c r="R4" t="n">
-        <v>7144663</v>
+        <v>7144719</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +999,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536258</v>
+        <v>121536678</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1066,22 +1071,18 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475366</v>
+        <v>475664</v>
       </c>
       <c r="R5" t="n">
-        <v>7144547</v>
+        <v>7144434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretå.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,11 +1130,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536430</v>
+        <v>121536313</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1190,14 +1186,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475508</v>
+        <v>475355</v>
       </c>
       <c r="R6" t="n">
-        <v>7144723</v>
+        <v>7144560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,11 +1226,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536398</v>
+        <v>121536258</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,16 +1273,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1302,18 +1293,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R7" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,6 +1356,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536313</v>
+        <v>121536535</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1393,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475355</v>
+        <v>475567</v>
       </c>
       <c r="R8" t="n">
-        <v>7144560</v>
+        <v>7144634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,19 +1462,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1488,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121535315</v>
+        <v>121536378</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1528,17 +1532,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475609</v>
+        <v>475462</v>
       </c>
       <c r="R9" t="n">
-        <v>7144719</v>
+        <v>7144663</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,11 +1574,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hack av tretå.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1583,11 +1582,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1604,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536845</v>
+        <v>121536352</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,16 +1614,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1644,14 +1638,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475736</v>
+        <v>475304</v>
       </c>
       <c r="R10" t="n">
-        <v>7144377</v>
+        <v>7144544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,6 +1678,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536535</v>
+        <v>121536845</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,41 +1725,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475567</v>
+        <v>475736</v>
       </c>
       <c r="R11" t="n">
-        <v>7144634</v>
+        <v>7144377</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,18 +1791,12 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536352</v>
+        <v>121536398</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,16 +1831,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1869,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475304</v>
+        <v>475462</v>
       </c>
       <c r="R12" t="n">
-        <v>7144544</v>
+        <v>7144663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1899,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,7 +1926,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536678</v>
+        <v>121536430</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1976,14 +1966,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475664</v>
+        <v>475508</v>
       </c>
       <c r="R13" t="n">
-        <v>7144434</v>
+        <v>7144723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,6 +2021,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2047,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549938</v>
+        <v>121548843</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,42 +2058,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475457</v>
+        <v>475702</v>
       </c>
       <c r="R14" t="n">
-        <v>7144705</v>
+        <v>7144555</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2135,7 +2125,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,6 +2134,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2162,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121548656</v>
+        <v>121550183</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,16 +2169,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2198,21 +2189,29 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475616</v>
+        <v>475609</v>
       </c>
       <c r="R15" t="n">
-        <v>7144593</v>
+        <v>7144648</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2246,7 +2245,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,11 +2256,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2278,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121548843</v>
+        <v>121549911</v>
       </c>
       <c r="B16" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,40 +2288,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R16" t="n">
-        <v>7144555</v>
+        <v>7144615</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2359,20 +2358,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2389,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549911</v>
+        <v>121548711</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,20 +2399,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2422,25 +2420,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475416</v>
+        <v>475702</v>
       </c>
       <c r="R17" t="n">
-        <v>7144615</v>
+        <v>7144662</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2473,6 +2471,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121550183</v>
+        <v>121548656</v>
       </c>
       <c r="B18" t="n">
-        <v>56561</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,16 +2523,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2540,29 +2543,21 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475609</v>
+        <v>475616</v>
       </c>
       <c r="R18" t="n">
-        <v>7144648</v>
+        <v>7144593</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2591,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,6 +2602,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548711</v>
+        <v>121549938</v>
       </c>
       <c r="B19" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,20 +2635,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2656,28 +2656,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475702</v>
+        <v>475457</v>
       </c>
       <c r="R19" t="n">
-        <v>7144662</v>
+        <v>7144705</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,11 +2722,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121535315</v>
+        <v>121536535</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +935,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475609</v>
+        <v>475567</v>
       </c>
       <c r="R4" t="n">
-        <v>7144719</v>
+        <v>7144634</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1015,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1035,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536678</v>
+        <v>121536376</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1075,14 +1074,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475664</v>
+        <v>475462</v>
       </c>
       <c r="R5" t="n">
-        <v>7144434</v>
+        <v>7144663</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,11 +1116,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1130,6 +1124,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1146,7 +1145,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121536313</v>
+        <v>121535315</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1186,17 +1185,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475355</v>
+        <v>475609</v>
       </c>
       <c r="R6" t="n">
-        <v>7144560</v>
+        <v>7144719</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,6 +1225,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536258</v>
+        <v>121536313</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1293,22 +1297,18 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475366</v>
+        <v>475355</v>
       </c>
       <c r="R7" t="n">
-        <v>7144547</v>
+        <v>7144560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,11 +1341,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536535</v>
+        <v>121536398</v>
       </c>
       <c r="B8" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,30 +1388,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1424,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475567</v>
+        <v>475462</v>
       </c>
       <c r="R8" t="n">
-        <v>7144634</v>
+        <v>7144663</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1456,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1465,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1492,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536378</v>
+        <v>121536258</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1528,18 +1519,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R9" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,6 +1569,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1582,6 +1582,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1598,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536352</v>
+        <v>121536678</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1638,14 +1643,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475304</v>
+        <v>475664</v>
       </c>
       <c r="R10" t="n">
-        <v>7144544</v>
+        <v>7144434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1687,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536845</v>
+        <v>121536430</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,16 +1730,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1749,14 +1754,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475736</v>
+        <v>475508</v>
       </c>
       <c r="R11" t="n">
-        <v>7144377</v>
+        <v>7144723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,6 +1796,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1799,6 +1809,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1815,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536398</v>
+        <v>121536352</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1859,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475462</v>
+        <v>475304</v>
       </c>
       <c r="R12" t="n">
-        <v>7144663</v>
+        <v>7144544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1914,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536430</v>
+        <v>121536845</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,16 +1957,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1966,14 +1981,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475508</v>
+        <v>475736</v>
       </c>
       <c r="R13" t="n">
-        <v>7144723</v>
+        <v>7144377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,11 +2023,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2021,11 +2031,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121548843</v>
+        <v>121549911</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,40 +2063,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R14" t="n">
-        <v>7144555</v>
+        <v>7144615</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2123,20 +2133,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2272,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121549911</v>
+        <v>121548843</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,45 +2297,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475416</v>
+        <v>475702</v>
       </c>
       <c r="R16" t="n">
-        <v>7144615</v>
+        <v>7144555</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2358,19 +2362,20 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2507,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548656</v>
+        <v>121549938</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,16 +2528,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2543,18 +2548,22 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475616</v>
+        <v>475457</v>
       </c>
       <c r="R18" t="n">
-        <v>7144593</v>
+        <v>7144705</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,7 +2600,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,11 +2611,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2623,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549938</v>
+        <v>121548656</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,16 +2643,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2659,22 +2663,18 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475457</v>
+        <v>475616</v>
       </c>
       <c r="R19" t="n">
-        <v>7144705</v>
+        <v>7144593</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,6 +2722,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536535</v>
+        <v>121536845</v>
       </c>
       <c r="B4" t="n">
-        <v>79698</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,41 +935,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475567</v>
+        <v>475736</v>
       </c>
       <c r="R4" t="n">
-        <v>7144634</v>
+        <v>7144377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,18 +1001,12 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536376</v>
+        <v>121536258</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1070,18 +1061,22 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475462</v>
+        <v>475366</v>
       </c>
       <c r="R5" t="n">
-        <v>7144663</v>
+        <v>7144547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,6 +1109,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536313</v>
+        <v>121536678</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1301,14 +1301,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475355</v>
+        <v>475664</v>
       </c>
       <c r="R7" t="n">
-        <v>7144560</v>
+        <v>7144434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,6 +1343,11 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flertalet färska tretåhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,11 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536258</v>
+        <v>121536378</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1519,22 +1519,18 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475366</v>
+        <v>475462</v>
       </c>
       <c r="R9" t="n">
-        <v>7144547</v>
+        <v>7144663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,11 +1565,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretå.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1582,11 +1573,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1603,7 +1589,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536678</v>
+        <v>121536313</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1643,14 +1629,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475664</v>
+        <v>475355</v>
       </c>
       <c r="R10" t="n">
-        <v>7144434</v>
+        <v>7144560</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,11 +1671,6 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flertalet färska tretåhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1698,6 +1679,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1830,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536352</v>
+        <v>121536535</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,27 +1832,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1874,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475304</v>
+        <v>475567</v>
       </c>
       <c r="R12" t="n">
-        <v>7144544</v>
+        <v>7144634</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,6 +1912,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1941,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536845</v>
+        <v>121536352</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1981,14 +1971,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475736</v>
+        <v>475304</v>
       </c>
       <c r="R13" t="n">
-        <v>7144377</v>
+        <v>7144544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,6 +2011,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121549911</v>
+        <v>121548656</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,16 +2058,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2083,11 +2078,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2095,13 +2086,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475416</v>
+        <v>475616</v>
       </c>
       <c r="R14" t="n">
-        <v>7144615</v>
+        <v>7144593</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,6 +2122,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121550183</v>
+        <v>121549938</v>
       </c>
       <c r="B15" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,16 +2174,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2203,24 +2199,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475609</v>
+        <v>475457</v>
       </c>
       <c r="R15" t="n">
-        <v>7144648</v>
+        <v>7144705</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2384,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121548711</v>
+        <v>121549911</v>
       </c>
       <c r="B17" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,20 +2396,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2425,25 +2417,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475702</v>
+        <v>475416</v>
       </c>
       <c r="R17" t="n">
-        <v>7144662</v>
+        <v>7144615</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2476,11 +2468,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121549938</v>
+        <v>121550183</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,16 +2515,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2553,20 +2540,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475457</v>
+        <v>475609</v>
       </c>
       <c r="R18" t="n">
-        <v>7144705</v>
+        <v>7144648</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2600,7 +2591,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548656</v>
+        <v>121548711</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57468</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,20 +2630,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2660,24 +2651,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R19" t="n">
-        <v>7144593</v>
+        <v>7144662</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2711,7 +2706,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536535</v>
+        <v>121536352</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,30 +1832,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1863,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475567</v>
+        <v>475304</v>
       </c>
       <c r="R12" t="n">
-        <v>7144634</v>
+        <v>7144544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1900,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1931,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536352</v>
+        <v>121536535</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,27 +1943,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1975,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475304</v>
+        <v>475567</v>
       </c>
       <c r="R13" t="n">
-        <v>7144544</v>
+        <v>7144634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tretåig hackspett.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,6 +2023,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121548656</v>
+        <v>121548711</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>57468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,20 +2054,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2075,24 +2075,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475616</v>
+        <v>475702</v>
       </c>
       <c r="R14" t="n">
-        <v>7144593</v>
+        <v>7144662</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,7 +2130,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121549938</v>
+        <v>121548656</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,16 +2178,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2194,22 +2198,18 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475457</v>
+        <v>475616</v>
       </c>
       <c r="R15" t="n">
-        <v>7144705</v>
+        <v>7144593</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,6 +2257,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2273,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121548843</v>
+        <v>121550183</v>
       </c>
       <c r="B16" t="n">
-        <v>79698</v>
+        <v>56561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,40 +2294,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475702</v>
+        <v>475609</v>
       </c>
       <c r="R16" t="n">
-        <v>7144555</v>
+        <v>7144648</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2356,7 +2370,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,7 +2379,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2499,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121550183</v>
+        <v>121548843</v>
       </c>
       <c r="B18" t="n">
-        <v>56561</v>
+        <v>79698</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,49 +2528,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475609</v>
+        <v>475702</v>
       </c>
       <c r="R18" t="n">
-        <v>7144648</v>
+        <v>7144555</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,7 +2595,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,6 +2604,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2618,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121548711</v>
+        <v>121549938</v>
       </c>
       <c r="B19" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,20 +2635,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2651,28 +2656,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475702</v>
+        <v>475457</v>
       </c>
       <c r="R19" t="n">
-        <v>7144662</v>
+        <v>7144705</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2711,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,11 +2722,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076523</v>
+        <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>91652</v>
+        <v>75140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,16 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>1467</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R25" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076489</v>
+        <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>75080</v>
+        <v>91726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3380,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R26" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>82855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>82852</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
         <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B24" t="n">
-        <v>91321</v>
+        <v>75143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R24" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B25" t="n">
-        <v>75143</v>
+        <v>91321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R25" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>75143</v>
+        <v>91322</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R24" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>91321</v>
+        <v>75143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R25" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076509</v>
+        <v>127076523</v>
       </c>
       <c r="B24" t="n">
-        <v>91322</v>
+        <v>91733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3264,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B25" t="n">
-        <v>75143</v>
+        <v>91322</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3270,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R25" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3369,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076523</v>
+        <v>127076489</v>
       </c>
       <c r="B26" t="n">
-        <v>91733</v>
+        <v>75143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,16 +3375,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>1467</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R26" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076523</v>
+        <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91733</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,16 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>1108</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>91322</v>
+        <v>75147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R25" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076489</v>
+        <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>75143</v>
+        <v>91737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3380,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R26" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076509</v>
+        <v>127076523</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>91737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3369,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076523</v>
+        <v>127076509</v>
       </c>
       <c r="B26" t="n">
-        <v>91737</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,16 +3375,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076523</v>
+        <v>127076489</v>
       </c>
       <c r="B24" t="n">
-        <v>91737</v>
+        <v>75147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,16 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>1467</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R24" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3259,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B25" t="n">
-        <v>75147</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R25" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076509</v>
+        <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>91737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3380,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>75147</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R24" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>75147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R25" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>75149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R24" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076489</v>
+        <v>127076509</v>
       </c>
       <c r="B25" t="n">
-        <v>75147</v>
+        <v>91328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R25" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076489</v>
+        <v>127076523</v>
       </c>
       <c r="B24" t="n">
-        <v>75149</v>
+        <v>91739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,21 +3170,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R24" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076523</v>
+        <v>127076489</v>
       </c>
       <c r="B26" t="n">
-        <v>91739</v>
+        <v>75149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,16 +3375,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>1467</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R26" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076523</v>
+        <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91739</v>
+        <v>91328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,16 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>1108</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076509</v>
+        <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>91328</v>
+        <v>75149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,21 +3275,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475344</v>
+        <v>475442</v>
       </c>
       <c r="R25" t="n">
-        <v>7144675</v>
+        <v>7144612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076489</v>
+        <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>75149</v>
+        <v>91739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3380,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475442</v>
+        <v>475344</v>
       </c>
       <c r="R26" t="n">
-        <v>7144612</v>
+        <v>7144675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B23" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
         <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076504</v>
+        <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>82861</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076502</v>
+        <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>82864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,21 +3065,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
         <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>75149</v>
+        <v>75152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>127076481</v>
       </c>
       <c r="B20" t="n">
-        <v>80127</v>
+        <v>80115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>127076492</v>
       </c>
       <c r="B21" t="n">
-        <v>91359</v>
+        <v>91337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>127076502</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>127076504</v>
       </c>
       <c r="B23" t="n">
-        <v>82864</v>
+        <v>82852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>127076509</v>
       </c>
       <c r="B24" t="n">
-        <v>91337</v>
+        <v>91315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>127076489</v>
       </c>
       <c r="B25" t="n">
-        <v>75152</v>
+        <v>75140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>127076523</v>
       </c>
       <c r="B26" t="n">
-        <v>91748</v>
+        <v>91726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>127076524</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>91319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>127076477</v>
       </c>
       <c r="B28" t="n">
-        <v>80127</v>
+        <v>80115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434312</v>
+        <v>127076509</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aron-Aronsabäcken, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475398</v>
+        <v>475344</v>
       </c>
       <c r="R2" t="n">
-        <v>7144723</v>
+        <v>7144675</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,35 +760,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Örtrik, bördig gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121434390</v>
+        <v>127076524</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,47 +791,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aron-Aronsabäcken, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475300</v>
+        <v>475344</v>
       </c>
       <c r="R3" t="n">
-        <v>7144605</v>
+        <v>7144675</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tydliga ringhack av Tretåig hackspett.</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,35 +865,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Fjällskog</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Örtrik, bördig gransumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121536845</v>
+        <v>127076504</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,38 +896,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475736</v>
+        <v>475330</v>
       </c>
       <c r="R4" t="n">
-        <v>7144377</v>
+        <v>7144518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,31 +969,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrik, bördig gransumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121536258</v>
+        <v>127076489</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,42 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Aron-Aronsa, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475366</v>
+        <v>475442</v>
       </c>
       <c r="R5" t="n">
-        <v>7144547</v>
+        <v>7144612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,17 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretå.</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,35 +1075,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik, bördig gransumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121535315</v>
+        <v>121536535</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,41 +1106,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Nyslåttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475609</v>
+        <v>475567</v>
       </c>
       <c r="R6" t="n">
-        <v>7144719</v>
+        <v>7144634</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack av tretå.</t>
+          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,13 +1186,9 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1261,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121536678</v>
+        <v>121548843</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,27 +1216,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475664</v>
+        <v>475702</v>
       </c>
       <c r="R7" t="n">
-        <v>7144434</v>
+        <v>7144555</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1283,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet färska tretåhack</t>
+          <t>Rikligt med skrovellav på gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,6 +1292,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121536398</v>
+        <v>127076477</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,38 +1322,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475462</v>
+        <v>475531</v>
       </c>
       <c r="R8" t="n">
-        <v>7144663</v>
+        <v>7144596</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,17 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår av spillkråka på samma gran som tretå.</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,33 +1393,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gles, lövrik grannaturskog i högläge, sannolikt tidigare fäbodskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121536378</v>
+        <v>127076481</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,38 +1428,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475462</v>
+        <v>475600</v>
       </c>
       <c r="R9" t="n">
-        <v>7144663</v>
+        <v>7144654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,12 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,72 +1499,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gles, lövrik grannaturskog i högläge, sannolikt tidigare fäbodskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121536313</v>
+        <v>127076502</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aron Aronsa, Jmt</t>
+          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475355</v>
+        <v>475330</v>
       </c>
       <c r="R10" t="n">
-        <v>7144560</v>
+        <v>7144518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,12 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,52 +1608,47 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Örtrik, bördig gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>A Karlssson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121536430</v>
+        <v>121536398</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1744,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475508</v>
+        <v>475462</v>
       </c>
       <c r="R11" t="n">
-        <v>7144723</v>
+        <v>7144663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1707,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flertalet färska ringhack av tretåig hackspett.</t>
+          <t>Spår av spillkråka på samma gran som tretå.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,11 +1718,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1816,32 +1734,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121536352</v>
+        <v>121536845</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1856,14 +1769,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475304</v>
+        <v>475736</v>
       </c>
       <c r="R12" t="n">
-        <v>7144544</v>
+        <v>7144377</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,11 +1809,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,46 +1835,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121536535</v>
+        <v>121548656</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1974,13 +1874,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475567</v>
+        <v>475616</v>
       </c>
       <c r="R13" t="n">
-        <v>7144634</v>
+        <v>7144593</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +1914,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gammal sälg med flertalet bålar av skrovellav.</t>
+          <t>Spillkråka spår av födosök på död stående gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,9 +1923,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2042,32 +1946,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121548711</v>
+        <v>121434312</v>
       </c>
       <c r="B14" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2075,28 +1974,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron-Aronsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475702</v>
+        <v>475398</v>
       </c>
       <c r="R14" t="n">
-        <v>7144662</v>
+        <v>7144723</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,17 +2021,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosökande lavskrikor 2 st.</t>
+          <t>Tydliga ringhack av Tretåig hackspett. Ev. Också födösök av Spillkråka på samma träd. Se bild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,15 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121548656</v>
+        <v>121434390</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,16 +2074,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2196,23 +2092,29 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475616</v>
+        <v>475300</v>
       </c>
       <c r="R15" t="n">
-        <v>7144593</v>
+        <v>7144605</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,17 +2138,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråka spår av födosök på död stående gran.</t>
+          <t>Tydliga ringhack av Tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2162,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Fjällskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2278,15 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121550183</v>
+        <v>121535315</v>
       </c>
       <c r="B16" t="n">
-        <v>56561</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,16 +2191,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2314,26 +2211,18 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Nedre Nyslåttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>475609</v>
       </c>
       <c r="R16" t="n">
-        <v>7144648</v>
+        <v>7144719</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Uppflygande Järpe samt färska spår i snön.</t>
+          <t>Färska hack av tretå.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,6 +2270,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2397,15 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121549911</v>
+        <v>121536258</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,23 +2324,23 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aron aronsa, Jmt</t>
+          <t>Aron-Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475416</v>
+        <v>475366</v>
       </c>
       <c r="R17" t="n">
-        <v>7144615</v>
+        <v>7144547</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2481,6 +2370,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretå.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,15 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121548843</v>
+        <v>121536313</v>
       </c>
       <c r="B18" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,40 +2417,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nyslåttjärnarna, Jmt</t>
+          <t>Aron Aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475702</v>
+        <v>475355</v>
       </c>
       <c r="R18" t="n">
-        <v>7144555</v>
+        <v>7144560</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,20 +2483,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav på gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2623,15 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121549938</v>
+        <v>121536352</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,25 +2543,21 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>aron aronsa, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475457</v>
+        <v>475304</v>
       </c>
       <c r="R19" t="n">
-        <v>7144705</v>
+        <v>7144544</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2711,7 +2591,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett.</t>
+          <t>Ringhack tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127076481</v>
+        <v>121536376</v>
       </c>
       <c r="B20" t="n">
-        <v>80127</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,37 +2629,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475600</v>
+        <v>475462</v>
       </c>
       <c r="R20" t="n">
-        <v>7144654</v>
+        <v>7144663</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,12 +2687,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2820,34 +2701,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Gles, lövrik grannaturskog i högläge, sannolikt tidigare fäbodskog</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127076492</v>
+        <v>121536430</v>
       </c>
       <c r="B21" t="n">
-        <v>91359</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,37 +2735,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475442</v>
+        <v>475508</v>
       </c>
       <c r="R21" t="n">
-        <v>7144612</v>
+        <v>7144723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,12 +2793,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flertalet färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,30 +2815,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127076502</v>
+        <v>121536678</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,37 +2846,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475330</v>
+        <v>475664</v>
       </c>
       <c r="R22" t="n">
-        <v>7144518</v>
+        <v>7144434</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,12 +2904,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flertalet färska tretåhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,31 +2925,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127076504</v>
+        <v>121549911</v>
       </c>
       <c r="B23" t="n">
-        <v>82864</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,40 +2952,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475330</v>
+        <v>475416</v>
       </c>
       <c r="R23" t="n">
-        <v>7144518</v>
+        <v>7144615</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,12 +3014,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,30 +3031,30 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127076509</v>
+        <v>121549938</v>
       </c>
       <c r="B24" t="n">
-        <v>91337</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,40 +3062,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>aron aronsa, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475344</v>
+        <v>475457</v>
       </c>
       <c r="R24" t="n">
-        <v>7144675</v>
+        <v>7144705</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,12 +3124,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,72 +3145,76 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127076489</v>
+        <v>121550183</v>
       </c>
       <c r="B25" t="n">
-        <v>75152</v>
+        <v>57132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475442</v>
+        <v>475609</v>
       </c>
       <c r="R25" t="n">
-        <v>7144612</v>
+        <v>7144648</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3332,12 +3238,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Uppflygande Järpe samt färska spår i snön.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,31 +3259,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076523</v>
+        <v>121548711</v>
       </c>
       <c r="B26" t="n">
-        <v>91748</v>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,35 +3286,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
+          <t>Nyslåttjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475344</v>
+        <v>475702</v>
       </c>
       <c r="R26" t="n">
-        <v>7144675</v>
+        <v>7144662</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3432,12 +3348,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökande lavskrikor 2 st.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3449,30 +3370,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Örtrik, bördig gransumpskog</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>A Karlssson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127076524</v>
+        <v>127076523</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>92329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,21 +3401,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3572,112 +3493,6 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>127076477</v>
-      </c>
-      <c r="B28" t="n">
-        <v>80127</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Naturskog vid Nedre Nyslåtttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>475531</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7144596</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Gles, lövrik grannaturskog i högläge, sannolikt tidigare fäbodskog</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4866-2024 artfynd.xlsx
+++ b/artfynd/A 4866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076509</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536535</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076481</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076502</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536398</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536845</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121434312</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121434390</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121535315</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536258</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536313</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536352</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536376</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,6 +3043,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121536678</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3048,6 +3158,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549911</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,6 +3273,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121549938</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3272,6 +3392,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121550183</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3387,6 +3512,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548711</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3492,8 +3622,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127076523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>